--- a/templates/bank_loan/CMA_Dashboard_Premium.xlsx
+++ b/templates/bank_loan/CMA_Dashboard_Premium.xlsx
@@ -4569,23 +4569,23 @@
         </is>
       </c>
       <c r="C25" s="327">
-        <f>IFERROR(C16/AVERAGE(C14,C17),0)</f>
+        <f>IFERROR(C16/IF(C14=0,C17,AVERAGE(C14,C17)),0)</f>
         <v/>
       </c>
       <c r="D25" s="327">
-        <f>IFERROR(D16/AVERAGE(D14,D17),0)</f>
+        <f>IFERROR(D16/IF(D14=0,D17,AVERAGE(D14,D17)),0)</f>
         <v/>
       </c>
       <c r="E25" s="327">
-        <f>IFERROR(E16/AVERAGE(E14,E17),0)</f>
+        <f>IFERROR(E16/IF(E14=0,E17,AVERAGE(E14,E17)),0)</f>
         <v/>
       </c>
       <c r="F25" s="327">
-        <f>IFERROR(F16/AVERAGE(F14,F17),0)</f>
+        <f>IFERROR(F16/IF(F14=0,F17,AVERAGE(F14,F17)),0)</f>
         <v/>
       </c>
       <c r="G25" s="327">
-        <f>IFERROR(G16/AVERAGE(G14,G17),0)</f>
+        <f>IFERROR(G16/IF(G14=0,G17,AVERAGE(G14,G17)),0)</f>
         <v/>
       </c>
     </row>
@@ -12923,51 +12923,51 @@
         </is>
       </c>
       <c r="B7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$C$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!C$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$C$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!C$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="C7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$C$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!D$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$C$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!D$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="D7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$C$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!E$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$C$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!E$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="E7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$C$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!F$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$C$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!F$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="F7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$C$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!G$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$C$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!G$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="G7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$C$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!H$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$C$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!H$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="H7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$C$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!I$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$C$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!I$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="I7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$C$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!J$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$C$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!J$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="J7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$C$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!K$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$C$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!K$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="K7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$C$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!L$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$C$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!L$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="L7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$C$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!M$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$C$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!M$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="M7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$C$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!N$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$C$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!N$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="N7" s="272">
@@ -12975,51 +12975,51 @@
         <v/>
       </c>
       <c r="O7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$D$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!C$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$D$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!C$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="P7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$D$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!D$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$D$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!D$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="Q7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$D$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!E$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$D$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!E$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="R7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$D$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!F$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$D$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!F$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="S7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$D$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!G$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$D$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!G$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="T7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$D$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!H$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$D$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!H$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="U7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$D$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!I$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$D$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!I$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="V7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$D$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!J$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$D$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!J$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="W7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$D$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!K$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$D$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!K$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="X7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$D$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!L$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$D$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!L$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="Y7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$D$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!M$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$D$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!M$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="Z7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$D$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!N$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$D$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!N$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="AA7" s="272">
@@ -13027,51 +13027,51 @@
         <v/>
       </c>
       <c r="AB7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$E$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!C$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$E$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!C$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="AC7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$E$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!D$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$E$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!D$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="AD7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$E$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!E$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$E$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!E$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="AE7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$E$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!F$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$E$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!F$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="AF7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$E$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!G$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$E$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!G$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="AG7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$E$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!H$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$E$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!H$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="AH7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$E$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!I$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$E$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!I$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="AI7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$E$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!J$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$E$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!J$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="AJ7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$E$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!K$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$E$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!K$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="AK7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$E$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!L$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$E$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!L$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="AL7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$E$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!M$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$E$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!M$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="AM7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$E$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!N$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$E$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!N$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="AN7" s="272">
@@ -13079,51 +13079,51 @@
         <v/>
       </c>
       <c r="AO7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$F$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!C$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$F$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!C$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="AP7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$F$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!D$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$F$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!D$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="AQ7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$F$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!E$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$F$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!E$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="AR7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$F$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!F$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$F$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!F$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="AS7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$F$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!G$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$F$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!G$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="AT7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$F$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!H$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$F$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!H$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="AU7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$F$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!I$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$F$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!I$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="AV7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$F$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!J$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$F$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!J$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="AW7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$F$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!K$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$F$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!K$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="AX7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$F$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!L$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$F$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!L$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="AY7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$F$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!M$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$F$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!M$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="AZ7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$F$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!N$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$F$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!N$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="BA7" s="272">
@@ -13131,51 +13131,51 @@
         <v/>
       </c>
       <c r="BB7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$G$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!C$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$G$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!C$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="BC7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$G$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!D$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$G$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!D$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="BD7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$G$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!E$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$G$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!E$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="BE7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$G$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!F$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$G$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!F$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="BF7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$G$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!G$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$G$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!G$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="BG7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$G$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!H$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$G$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!H$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="BH7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$G$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!I$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$G$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!I$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="BI7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$G$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!J$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$G$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!J$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="BJ7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$G$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!K$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$G$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!K$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="BK7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$G$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!L$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$G$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!L$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="BL7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$G$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!M$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$G$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!M$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="BM7" s="272">
-        <f>(Assumptions!$C$16*Assumptions!$G$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!N$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>MIN(Assumptions!$C$16/12,(Assumptions!$C$16*Assumptions!$G$18/12)*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!N$21/SUM(Assumptions!$C$21:$N$21)))</f>
         <v/>
       </c>
       <c r="BN7" s="272">
